--- a/temp_result/[238010] sales academy/[238010] sales academy.xlsx
+++ b/temp_result/[238010] sales academy/[238010] sales academy.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="340">
   <si>
     <t>Référence</t>
   </si>
@@ -178,9 +178,6 @@
     <t>Mission_Clean</t>
   </si>
   <si>
-    <t>MissionLib</t>
-  </si>
-  <si>
     <t>10941</t>
   </si>
   <si>
@@ -208,12 +205,12 @@
     <t>10926</t>
   </si>
   <si>
+    <t>10933</t>
+  </si>
+  <si>
     <t>10557</t>
   </si>
   <si>
-    <t>10933</t>
-  </si>
-  <si>
     <t>10358</t>
   </si>
   <si>
@@ -325,6 +322,51 @@
     <t>11636</t>
   </si>
   <si>
+    <t>11812</t>
+  </si>
+  <si>
+    <t>11814</t>
+  </si>
+  <si>
+    <t>11817</t>
+  </si>
+  <si>
+    <t>11819</t>
+  </si>
+  <si>
+    <t>11820</t>
+  </si>
+  <si>
+    <t>11832</t>
+  </si>
+  <si>
+    <t>11980</t>
+  </si>
+  <si>
+    <t>11955</t>
+  </si>
+  <si>
+    <t>11956</t>
+  </si>
+  <si>
+    <t>11904</t>
+  </si>
+  <si>
+    <t>12049</t>
+  </si>
+  <si>
+    <t>12048</t>
+  </si>
+  <si>
+    <t>11958</t>
+  </si>
+  <si>
+    <t>11977</t>
+  </si>
+  <si>
+    <t>11957</t>
+  </si>
+  <si>
     <t>Parking</t>
   </si>
   <si>
@@ -349,12 +391,12 @@
     <t>Train aller</t>
   </si>
   <si>
+    <t>Train retour</t>
+  </si>
+  <si>
     <t>mar. 8 juil. 2025 Creys-Mépieu-Mercurol</t>
   </si>
   <si>
-    <t>Train retour</t>
-  </si>
-  <si>
     <t>Scan 08/07 13:44:23</t>
   </si>
   <si>
@@ -418,6 +460,36 @@
     <t>TA Suivi Fouad ALKHOURY Scan 31/10 08:52:13</t>
   </si>
   <si>
+    <t>Train Domicile &gt; Tain</t>
+  </si>
+  <si>
+    <t>Taxi Tain Gare &gt; Valrhona</t>
+  </si>
+  <si>
+    <t>Dejeuner Tain</t>
+  </si>
+  <si>
+    <t>Diner Tain Sales Academy</t>
+  </si>
+  <si>
+    <t>Facture Hotel Tain_Sales Academy</t>
+  </si>
+  <si>
+    <t>Taxi Tain &gt; Gare Valence TGV</t>
+  </si>
+  <si>
+    <t>IK 25-11-25</t>
+  </si>
+  <si>
+    <t>PEAGE ALLER TAIN LHERMITAGE - DOMICILE</t>
+  </si>
+  <si>
+    <t>PEAGE RETOUR TAIN LHERMITAGE - DOMICILE</t>
+  </si>
+  <si>
+    <t>Train</t>
+  </si>
+  <si>
     <t>Transport</t>
   </si>
   <si>
@@ -433,6 +505,9 @@
     <t>HOTEL GRANDE AGGLO FDV</t>
   </si>
   <si>
+    <t>Péage</t>
+  </si>
+  <si>
     <t>EUR</t>
   </si>
   <si>
@@ -442,6 +517,9 @@
     <t>5.50%</t>
   </si>
   <si>
+    <t>20.00%</t>
+  </si>
+  <si>
     <t>Oui</t>
   </si>
   <si>
@@ -493,6 +571,27 @@
     <t>Le Commerce</t>
   </si>
   <si>
+    <t>Raph Taxi</t>
+  </si>
+  <si>
+    <t>Bar Le Tainois</t>
+  </si>
+  <si>
+    <t>Fac &amp; Spera</t>
+  </si>
+  <si>
+    <t>Asf</t>
+  </si>
+  <si>
+    <t>Asf Bourg-les-valence</t>
+  </si>
+  <si>
+    <t>Taxi Jean Marc</t>
+  </si>
+  <si>
+    <t>Area Direction Peage</t>
+  </si>
+  <si>
     <t>14 RUE DES MIMOSAS, VILLENEUVE LES MAGUELONE, 34750, France</t>
   </si>
   <si>
@@ -571,6 +670,24 @@
     <t>53 Rue de Marseille, Lyon, 69007, France</t>
   </si>
   <si>
+    <t>4 chemin de la digue, St Jean de muzols, 07300, France</t>
+  </si>
+  <si>
+    <t>1 avenue du Docteur Paul Durand, TAIN L'HERMITAGE, 26600, France</t>
+  </si>
+  <si>
+    <t>CEDEX, BOURG-LES-VALENCE, 26503, France</t>
+  </si>
+  <si>
+    <t>BP325 CEDEX, BOURG-LES-VALENCE, 26503, France</t>
+  </si>
+  <si>
+    <t>ST: Nº 10, MAUGUIO, France</t>
+  </si>
+  <si>
+    <t>22D avenue Lionel Terray, Jonage, 69330, France</t>
+  </si>
+  <si>
     <t>FR64383451267</t>
   </si>
   <si>
@@ -607,6 +724,18 @@
     <t>FR49839931128</t>
   </si>
   <si>
+    <t>FR57831082920</t>
+  </si>
+  <si>
+    <t>FR73508821345</t>
+  </si>
+  <si>
+    <t>FR82422311704</t>
+  </si>
+  <si>
+    <t>FR70328837844</t>
+  </si>
+  <si>
     <t>010725</t>
   </si>
   <si>
@@ -701,6 +830,48 @@
   </si>
   <si>
     <t>Fre_A1B35-A1B35015577/1</t>
+  </si>
+  <si>
+    <t>2037421882-20251116</t>
+  </si>
+  <si>
+    <t>MED7KYNU-425</t>
+  </si>
+  <si>
+    <t>001-002-202974</t>
+  </si>
+  <si>
+    <t>1009 1 191449</t>
+  </si>
+  <si>
+    <t>F42417</t>
+  </si>
+  <si>
+    <t>MED7KYNU-427</t>
+  </si>
+  <si>
+    <t>R3290858062030200030</t>
+  </si>
+  <si>
+    <t>R3291754252011100125</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>438563974</t>
+  </si>
+  <si>
+    <t>278998721</t>
+  </si>
+  <si>
+    <t>001-002-204369</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>202511250724018450183</t>
   </si>
   <si>
     <t>Preuve paiement parking 
@@ -749,6 +920,12 @@
     <t>Petit déjeuner</t>
   </si>
   <si>
+    <t>JOURNEE SALES ACADEMY 2026 VALRHONA</t>
+  </si>
+  <si>
+    <t>JOURNEE SALES ACADEMY TAIN LHERMITAGE</t>
+  </si>
+  <si>
     <t>Béatrice Chausson</t>
   </si>
   <si>
@@ -806,6 +983,15 @@
     <t>IK Octobre 2025 V2</t>
   </si>
   <si>
+    <t>NOVEMBRE 2025</t>
+  </si>
+  <si>
+    <t>Note de frais julie larue novembre 2025</t>
+  </si>
+  <si>
+    <t>2025_11_Béatrice Chausson</t>
+  </si>
+  <si>
     <t>À la compta</t>
   </si>
   <si>
@@ -815,7 +1001,13 @@
     <t>Lionel Gerfaud</t>
   </si>
   <si>
+    <t>Stéphane Skeirik</t>
+  </si>
+  <si>
     <t>Marketing</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
   <si>
     <t>ADVENT+</t>
@@ -1204,10 +1396,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BC49"/>
+  <dimension ref="A1:BB64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:55">
+    <row r="1" spans="1:54">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1370,22 +1562,19 @@
       <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:54">
+      <c r="A2" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:55">
-      <c r="A2" t="s">
-        <v>55</v>
       </c>
       <c r="B2" s="2">
         <v>45839</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="E2">
         <v>625100</v>
@@ -1409,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M2">
         <v>21.4</v>
@@ -1424,87 +1613,84 @@
         <v>1</v>
       </c>
       <c r="AA2" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB2" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC2" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="AD2" t="s">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="AE2" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="AF2" t="s">
-        <v>197</v>
+        <v>240</v>
       </c>
       <c r="AG2" t="s">
-        <v>229</v>
+        <v>286</v>
       </c>
       <c r="AJ2">
         <v>546</v>
       </c>
       <c r="AK2" t="s">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="AL2" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN2" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP2" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ2" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS2" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT2" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU2" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV2" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX2" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY2" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ2" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA2" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB2" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="3" spans="1:55">
+    <row r="3" spans="1:54">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2">
         <v>45839</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E3">
         <v>625100</v>
@@ -1528,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M3">
         <v>32</v>
@@ -1543,78 +1729,75 @@
         <v>1</v>
       </c>
       <c r="AA3" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB3" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AD3" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AF3" t="s">
-        <v>197</v>
+        <v>240</v>
       </c>
       <c r="AJ3">
         <v>546</v>
       </c>
       <c r="AK3" t="s">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="AL3" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN3" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP3" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ3" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS3" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT3" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU3" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV3" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX3" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY3" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ3" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA3" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB3" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="4" spans="1:55">
+    <row r="4" spans="1:54">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2">
         <v>45839</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="E4">
         <v>625400</v>
@@ -1635,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M4">
         <v>22.83</v>
@@ -1647,69 +1830,66 @@
         <v>1</v>
       </c>
       <c r="AA4" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AD4" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="AJ4">
         <v>551</v>
       </c>
       <c r="AK4" t="s">
-        <v>249</v>
+        <v>308</v>
       </c>
       <c r="AL4" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN4" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP4" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ4" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS4" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT4" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU4" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV4" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX4" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AZ4" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA4" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB4" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="5" spans="1:55">
+    <row r="5" spans="1:54">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2">
         <v>45839</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E5">
         <v>625100</v>
@@ -1733,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M5">
         <v>54</v>
@@ -1748,81 +1928,78 @@
         <v>1</v>
       </c>
       <c r="AA5" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB5" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC5" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="AD5" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="AE5" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="AJ5">
         <v>521</v>
       </c>
       <c r="AK5" t="s">
-        <v>250</v>
+        <v>309</v>
       </c>
       <c r="AL5" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN5" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP5" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ5" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS5" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT5" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU5" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV5" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX5" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY5" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ5" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA5" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB5" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC5" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="6" spans="1:55">
+    <row r="6" spans="1:54">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2">
         <v>45839</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E6">
         <v>625100</v>
@@ -1846,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M6">
         <v>44</v>
@@ -1861,81 +2038,78 @@
         <v>1</v>
       </c>
       <c r="AA6" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB6" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC6" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="AD6" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="AE6" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="AJ6">
         <v>521</v>
       </c>
       <c r="AK6" t="s">
-        <v>250</v>
+        <v>309</v>
       </c>
       <c r="AL6" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN6" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP6" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ6" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS6" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT6" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU6" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV6" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX6" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY6" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ6" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA6" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB6" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="7" spans="1:55">
+    <row r="7" spans="1:54">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2">
         <v>45842</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E7">
         <v>625100</v>
@@ -1956,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M7">
         <v>73</v>
@@ -1971,87 +2145,84 @@
         <v>1</v>
       </c>
       <c r="AA7" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB7" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC7" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="AD7" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="AE7" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="AG7" t="s">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="AJ7">
         <v>488</v>
       </c>
       <c r="AK7" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="AL7" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN7" t="s">
-        <v>264</v>
+        <v>326</v>
       </c>
       <c r="AO7" t="s">
-        <v>266</v>
+        <v>329</v>
       </c>
       <c r="AP7" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ7" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS7" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT7" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU7" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV7" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX7" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY7" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ7" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA7" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB7" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="8" spans="1:55">
+    <row r="8" spans="1:54">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2">
         <v>45842</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E8">
         <v>625100</v>
@@ -2072,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M8">
         <v>73</v>
@@ -2087,87 +2258,84 @@
         <v>1</v>
       </c>
       <c r="AA8" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB8" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC8" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="AD8" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="AE8" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="AG8" t="s">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="AJ8">
         <v>488</v>
       </c>
       <c r="AK8" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="AL8" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN8" t="s">
-        <v>264</v>
+        <v>326</v>
       </c>
       <c r="AO8" t="s">
-        <v>266</v>
+        <v>329</v>
       </c>
       <c r="AP8" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ8" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS8" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT8" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU8" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV8" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX8" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY8" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ8" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA8" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB8" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="9" spans="1:55">
+    <row r="9" spans="1:54">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2">
         <v>45846</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E9">
         <v>625100</v>
@@ -2191,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M9">
         <v>44</v>
@@ -2206,84 +2374,81 @@
         <v>1</v>
       </c>
       <c r="AA9" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB9" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC9" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="AD9" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="AE9" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="AF9" t="s">
-        <v>198</v>
+        <v>241</v>
       </c>
       <c r="AJ9">
         <v>546</v>
       </c>
       <c r="AK9" t="s">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="AL9" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN9" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP9" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ9" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS9" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT9" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU9" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV9" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX9" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY9" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ9" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA9" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB9" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC9" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="10" spans="1:55">
+    <row r="10" spans="1:54">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" s="2">
         <v>45846</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="E10">
         <v>625100</v>
@@ -2307,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M10">
         <v>33.95</v>
@@ -2322,292 +2487,283 @@
         <v>1</v>
       </c>
       <c r="AA10" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB10" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AD10" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AG10" t="s">
-        <v>231</v>
+        <v>288</v>
       </c>
       <c r="AJ10">
         <v>546</v>
       </c>
       <c r="AK10" t="s">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="AL10" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN10" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP10" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ10" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS10" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT10" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU10" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV10" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX10" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ10" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA10" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB10" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC10" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="11" spans="1:55">
+    <row r="11" spans="1:54">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2">
         <v>45846</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="E11">
-        <v>625400</v>
+        <v>625100</v>
+      </c>
+      <c r="F11">
+        <v>445660</v>
       </c>
       <c r="G11">
-        <v>289.28</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>113.98</v>
+        <v>44</v>
       </c>
       <c r="I11">
-        <v>113.98</v>
+        <v>44</v>
       </c>
       <c r="J11">
-        <v>113.98</v>
+        <v>44</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M11">
-        <v>113.98</v>
+        <v>44</v>
       </c>
       <c r="N11">
-        <v>113.98</v>
+        <v>44</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
       </c>
       <c r="Z11">
         <v>1</v>
       </c>
       <c r="AA11" t="s">
-        <v>142</v>
+        <v>168</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>171</v>
       </c>
       <c r="AD11" t="s">
-        <v>163</v>
+        <v>195</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>225</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>242</v>
       </c>
       <c r="AJ11">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="AK11" t="s">
-        <v>252</v>
+        <v>307</v>
       </c>
       <c r="AL11" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN11" t="s">
-        <v>264</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="AP11" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ11" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS11" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT11" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU11" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV11" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX11" t="s">
-        <v>160</v>
+        <v>193</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>338</v>
       </c>
       <c r="AZ11" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA11" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB11" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC11" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="12" spans="1:55">
+    <row r="12" spans="1:54">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2">
         <v>45846</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="E12">
-        <v>625100</v>
-      </c>
-      <c r="F12">
-        <v>445660</v>
+        <v>625400</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>289.28</v>
       </c>
       <c r="H12">
-        <v>44</v>
+        <v>113.98</v>
       </c>
       <c r="I12">
-        <v>44</v>
+        <v>113.98</v>
       </c>
       <c r="J12">
-        <v>44</v>
+        <v>113.98</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M12">
-        <v>44</v>
+        <v>113.98</v>
       </c>
       <c r="N12">
-        <v>44</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
+        <v>113.98</v>
       </c>
       <c r="Z12">
         <v>1</v>
       </c>
       <c r="AA12" t="s">
-        <v>142</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>143</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="AD12" t="s">
-        <v>162</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>186</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="AJ12">
-        <v>546</v>
+        <v>525</v>
       </c>
       <c r="AK12" t="s">
-        <v>248</v>
+        <v>311</v>
       </c>
       <c r="AL12" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN12" t="s">
-        <v>244</v>
+        <v>326</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>329</v>
       </c>
       <c r="AP12" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ12" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS12" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT12" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU12" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV12" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX12" t="s">
-        <v>160</v>
-      </c>
-      <c r="AY12" t="s">
-        <v>274</v>
+        <v>193</v>
       </c>
       <c r="AZ12" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA12" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB12" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC12" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="13" spans="1:55">
+    <row r="13" spans="1:54">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2">
         <v>45846</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E13">
         <v>625300</v>
@@ -2631,7 +2787,7 @@
         <v>2.82</v>
       </c>
       <c r="L13" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M13">
         <v>31.05</v>
@@ -2640,7 +2796,7 @@
         <v>28.23</v>
       </c>
       <c r="O13" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="P13">
         <v>2.82</v>
@@ -2658,96 +2814,93 @@
         <v>3</v>
       </c>
       <c r="AA13" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB13" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC13" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="AD13" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="AE13" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="AF13" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="AH13" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AI13" t="s">
-        <v>246</v>
+        <v>305</v>
       </c>
       <c r="AJ13">
         <v>512</v>
       </c>
       <c r="AK13" t="s">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="AL13" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AM13" t="s">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="AN13" t="s">
-        <v>264</v>
+        <v>326</v>
       </c>
       <c r="AO13" t="s">
-        <v>266</v>
+        <v>329</v>
       </c>
       <c r="AP13" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ13" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS13" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT13" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU13" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV13" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX13" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY13" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ13" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA13" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB13" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC13" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="14" spans="1:55">
+    <row r="14" spans="1:54">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2">
         <v>45846</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="E14">
         <v>625100</v>
@@ -2771,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M14">
         <v>25</v>
@@ -2786,81 +2939,78 @@
         <v>1</v>
       </c>
       <c r="AA14" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB14" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC14" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="AD14" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="AF14" t="s">
-        <v>201</v>
+        <v>244</v>
       </c>
       <c r="AJ14">
         <v>546</v>
       </c>
       <c r="AK14" t="s">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="AL14" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN14" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP14" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ14" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS14" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT14" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU14" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV14" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX14" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY14" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ14" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA14" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB14" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC14" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="15" spans="1:55">
+    <row r="15" spans="1:54">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2">
         <v>45861</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="E15">
         <v>625400</v>
@@ -2881,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M15">
         <v>36.88</v>
@@ -2893,66 +3043,63 @@
         <v>1</v>
       </c>
       <c r="AA15" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AD15" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="AJ15">
         <v>526</v>
       </c>
       <c r="AK15" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="AL15" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN15" t="s">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="AP15" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AS15" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT15" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU15" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV15" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX15" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AZ15" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA15" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB15" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC15" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="16" spans="1:55">
+    <row r="16" spans="1:54">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2">
         <v>45874</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E16">
         <v>625100</v>
@@ -2976,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M16">
         <v>38</v>
@@ -2991,87 +3138,84 @@
         <v>1</v>
       </c>
       <c r="AA16" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB16" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC16" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="AD16" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="AE16" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="AF16" t="s">
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="AG16" t="s">
-        <v>232</v>
+        <v>289</v>
       </c>
       <c r="AJ16">
         <v>565</v>
       </c>
       <c r="AK16" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="AL16" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN16" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP16" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ16" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS16" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT16" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU16" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV16" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX16" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY16" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ16" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA16" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB16" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC16" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="17" spans="1:55">
+    <row r="17" spans="1:54">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2">
         <v>45874</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E17">
         <v>625100</v>
@@ -3095,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M17">
         <v>44</v>
@@ -3110,84 +3254,81 @@
         <v>1</v>
       </c>
       <c r="AA17" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB17" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC17" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="AD17" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="AF17" t="s">
-        <v>203</v>
+        <v>246</v>
       </c>
       <c r="AG17" t="s">
-        <v>232</v>
+        <v>289</v>
       </c>
       <c r="AJ17">
         <v>565</v>
       </c>
       <c r="AK17" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="AL17" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN17" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP17" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ17" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS17" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT17" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU17" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV17" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX17" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY17" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ17" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA17" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB17" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC17" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="18" spans="1:55">
+    <row r="18" spans="1:54">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2">
         <v>45874</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="E18">
         <v>625400</v>
@@ -3208,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M18">
         <v>113.98</v>
@@ -3220,75 +3361,72 @@
         <v>1</v>
       </c>
       <c r="AA18" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AD18" t="s">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s">
-        <v>233</v>
+        <v>290</v>
       </c>
       <c r="AJ18">
         <v>543</v>
       </c>
       <c r="AK18" t="s">
-        <v>256</v>
+        <v>315</v>
       </c>
       <c r="AL18" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN18" t="s">
-        <v>264</v>
+        <v>326</v>
       </c>
       <c r="AO18" t="s">
-        <v>266</v>
+        <v>329</v>
       </c>
       <c r="AP18" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ18" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS18" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT18" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU18" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV18" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX18" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AZ18" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA18" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB18" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC18" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:55">
+    <row r="19" spans="1:54">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B19" s="2">
         <v>45874</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="E19">
         <v>625400</v>
@@ -3309,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M19">
         <v>178.79</v>
@@ -3321,66 +3459,63 @@
         <v>1</v>
       </c>
       <c r="AA19" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AD19" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="AJ19">
         <v>566</v>
       </c>
       <c r="AK19" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="AL19" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN19" t="s">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="AP19" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AS19" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT19" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU19" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV19" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX19" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AZ19" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA19" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB19" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC19" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="20" spans="1:55">
+    <row r="20" spans="1:54">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B20" s="2">
         <v>45874</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E20">
         <v>625300</v>
@@ -3404,7 +3539,7 @@
         <v>2.38</v>
       </c>
       <c r="L20" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M20">
         <v>26.1</v>
@@ -3413,7 +3548,7 @@
         <v>23.72</v>
       </c>
       <c r="O20" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="P20">
         <v>2.38</v>
@@ -3431,96 +3566,93 @@
         <v>3</v>
       </c>
       <c r="AA20" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB20" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC20" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="AD20" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="AE20" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="AF20" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
       <c r="AG20" t="s">
-        <v>234</v>
+        <v>291</v>
       </c>
       <c r="AH20" t="s">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="AI20" t="s">
-        <v>247</v>
+        <v>306</v>
       </c>
       <c r="AJ20">
         <v>543</v>
       </c>
       <c r="AK20" t="s">
-        <v>256</v>
+        <v>315</v>
       </c>
       <c r="AL20" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN20" t="s">
-        <v>264</v>
+        <v>326</v>
       </c>
       <c r="AO20" t="s">
-        <v>266</v>
+        <v>329</v>
       </c>
       <c r="AP20" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ20" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS20" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT20" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU20" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV20" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX20" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY20" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ20" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA20" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB20" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC20" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="21" spans="1:55">
+    <row r="21" spans="1:54">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B21" s="2">
         <v>45874</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D21" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="E21">
         <v>625100</v>
@@ -3544,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M21">
         <v>70</v>
@@ -3559,87 +3691,84 @@
         <v>1</v>
       </c>
       <c r="AA21" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB21" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC21" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="AD21" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="AE21" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="AF21" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="AG21" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="AJ21">
         <v>565</v>
       </c>
       <c r="AK21" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="AL21" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN21" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP21" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ21" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS21" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT21" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU21" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV21" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX21" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY21" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ21" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA21" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB21" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC21" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="22" spans="1:55">
+    <row r="22" spans="1:54">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2">
         <v>45916</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E22">
         <v>625100</v>
@@ -3663,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M22">
         <v>44</v>
@@ -3678,84 +3807,81 @@
         <v>1</v>
       </c>
       <c r="AA22" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB22" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC22" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="AD22" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="AE22" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="AF22" t="s">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="AJ22">
         <v>570</v>
       </c>
       <c r="AK22" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="AL22" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN22" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP22" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ22" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS22" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT22" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU22" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV22" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX22" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY22" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ22" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA22" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB22" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC22" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="23" spans="1:55">
+    <row r="23" spans="1:54">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23" s="2">
         <v>45916</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E23">
         <v>625100</v>
@@ -3779,7 +3905,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M23">
         <v>44</v>
@@ -3794,84 +3920,81 @@
         <v>1</v>
       </c>
       <c r="AA23" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB23" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC23" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="AD23" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="AE23" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="AF23" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="AJ23">
         <v>570</v>
       </c>
       <c r="AK23" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="AL23" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN23" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP23" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ23" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS23" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT23" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU23" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV23" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX23" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY23" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ23" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA23" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB23" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC23" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="24" spans="1:55">
+    <row r="24" spans="1:54">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B24" s="2">
         <v>45916</v>
       </c>
       <c r="C24" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" t="s">
         <v>118</v>
-      </c>
-      <c r="D24" t="s">
-        <v>104</v>
       </c>
       <c r="E24">
         <v>625100</v>
@@ -3895,7 +4018,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M24">
         <v>70.8</v>
@@ -3904,7 +4027,7 @@
         <v>64.36</v>
       </c>
       <c r="O24" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="P24">
         <v>6.44</v>
@@ -3922,87 +4045,84 @@
         <v>1</v>
       </c>
       <c r="AA24" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB24" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC24" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="AD24" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="AE24" t="s">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="AF24" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s">
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="AJ24">
         <v>570</v>
       </c>
       <c r="AK24" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="AL24" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN24" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP24" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ24" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS24" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT24" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU24" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV24" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX24" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY24" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ24" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA24" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB24" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC24" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="25" spans="1:55">
+    <row r="25" spans="1:54">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2">
         <v>45923</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="E25">
         <v>625100</v>
@@ -4026,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M25">
         <v>36.3</v>
@@ -4035,7 +4155,7 @@
         <v>33</v>
       </c>
       <c r="O25" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="P25">
         <v>3.3</v>
@@ -4053,78 +4173,75 @@
         <v>1</v>
       </c>
       <c r="AA25" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB25" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC25" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="AD25" t="s">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="AJ25">
         <v>570</v>
       </c>
       <c r="AK25" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="AL25" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN25" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP25" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ25" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS25" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT25" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU25" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV25" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX25" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY25" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ25" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA25" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB25" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC25" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="26" spans="1:55">
+    <row r="26" spans="1:54">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2">
         <v>45923</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E26">
         <v>625100</v>
@@ -4148,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M26">
         <v>44</v>
@@ -4163,87 +4280,84 @@
         <v>1</v>
       </c>
       <c r="AA26" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB26" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC26" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="AD26" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="AE26" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="AF26" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s">
-        <v>236</v>
+        <v>293</v>
       </c>
       <c r="AJ26">
         <v>570</v>
       </c>
       <c r="AK26" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="AL26" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN26" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP26" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ26" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS26" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT26" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU26" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV26" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX26" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY26" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ26" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA26" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB26" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC26" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="27" spans="1:55">
+    <row r="27" spans="1:54">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B27" s="2">
         <v>45923</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E27">
         <v>625100</v>
@@ -4267,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M27">
         <v>44</v>
@@ -4282,84 +4396,81 @@
         <v>1</v>
       </c>
       <c r="AA27" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB27" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC27" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="AD27" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="AE27" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="AF27" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="AJ27">
         <v>570</v>
       </c>
       <c r="AK27" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="AL27" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN27" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP27" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ27" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS27" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT27" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU27" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV27" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX27" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY27" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ27" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA27" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB27" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC27" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="28" spans="1:55">
+    <row r="28" spans="1:54">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="2">
         <v>45923</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E28">
         <v>625300</v>
@@ -4383,7 +4494,7 @@
         <v>0.8</v>
       </c>
       <c r="L28" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M28">
         <v>8.75</v>
@@ -4392,7 +4503,7 @@
         <v>7.95</v>
       </c>
       <c r="O28" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="P28">
         <v>0.8</v>
@@ -4410,84 +4521,81 @@
         <v>1</v>
       </c>
       <c r="AA28" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB28" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC28" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="AD28" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="AE28" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="AF28" t="s">
-        <v>211</v>
+        <v>254</v>
       </c>
       <c r="AJ28">
         <v>570</v>
       </c>
       <c r="AK28" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="AL28" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN28" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP28" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ28" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS28" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT28" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU28" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV28" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX28" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY28" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ28" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA28" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB28" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC28" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="29" spans="1:55">
+    <row r="29" spans="1:54">
       <c r="A29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B29" s="2">
         <v>45923</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="E29">
         <v>625100</v>
@@ -4511,7 +4619,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M29">
         <v>34.8</v>
@@ -4520,7 +4628,7 @@
         <v>31.64</v>
       </c>
       <c r="O29" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="P29">
         <v>3.16</v>
@@ -4538,78 +4646,75 @@
         <v>1</v>
       </c>
       <c r="AA29" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB29" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC29" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="AD29" t="s">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="AJ29">
         <v>570</v>
       </c>
       <c r="AK29" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="AL29" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN29" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP29" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ29" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS29" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT29" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU29" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV29" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX29" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY29" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ29" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA29" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB29" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC29" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="30" spans="1:55">
+    <row r="30" spans="1:54">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B30" s="2">
         <v>45923</v>
       </c>
       <c r="C30" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" t="s">
         <v>118</v>
-      </c>
-      <c r="D30" t="s">
-        <v>104</v>
       </c>
       <c r="E30">
         <v>625100</v>
@@ -4633,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M30">
         <v>71.09999999999999</v>
@@ -4642,7 +4747,7 @@
         <v>64.64</v>
       </c>
       <c r="O30" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="P30">
         <v>6.46</v>
@@ -4660,84 +4765,81 @@
         <v>1</v>
       </c>
       <c r="AA30" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB30" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC30" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="AD30" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="AF30" t="s">
-        <v>212</v>
+        <v>255</v>
       </c>
       <c r="AG30" t="s">
-        <v>237</v>
+        <v>294</v>
       </c>
       <c r="AJ30">
         <v>570</v>
       </c>
       <c r="AK30" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="AL30" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN30" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP30" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ30" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS30" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT30" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU30" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV30" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX30" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY30" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ30" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA30" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB30" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC30" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="31" spans="1:55">
+    <row r="31" spans="1:54">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B31" s="2">
         <v>45937</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="E31">
         <v>625100</v>
@@ -4761,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M31">
         <v>35.95</v>
@@ -4770,7 +4872,7 @@
         <v>32.68</v>
       </c>
       <c r="O31" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="P31">
         <v>3.27</v>
@@ -4788,87 +4890,84 @@
         <v>1</v>
       </c>
       <c r="AA31" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB31" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC31" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="AD31" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="AE31" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="AF31" t="s">
-        <v>213</v>
+        <v>256</v>
       </c>
       <c r="AG31" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="AJ31">
         <v>583</v>
       </c>
       <c r="AK31" t="s">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="AL31" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN31" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP31" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ31" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS31" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT31" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU31" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV31" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX31" t="s">
-        <v>273</v>
+        <v>337</v>
       </c>
       <c r="AY31" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ31" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA31" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB31" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC31" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="32" spans="1:55">
+    <row r="32" spans="1:54">
       <c r="A32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B32" s="2">
         <v>45937</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D32" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="E32">
         <v>615100</v>
@@ -4889,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M32">
         <v>201.62</v>
@@ -4904,81 +5003,78 @@
         <v>1</v>
       </c>
       <c r="AA32" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB32" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AD32" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
       <c r="AG32" t="s">
-        <v>238</v>
+        <v>295</v>
       </c>
       <c r="AJ32">
         <v>584</v>
       </c>
       <c r="AK32" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="AL32" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN32" t="s">
-        <v>264</v>
+        <v>326</v>
       </c>
       <c r="AO32" t="s">
-        <v>266</v>
+        <v>329</v>
       </c>
       <c r="AP32" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ32" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS32" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT32" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU32" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV32" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX32" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY32" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ32" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA32" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB32" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC32" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="33" spans="1:55">
+    <row r="33" spans="1:54">
       <c r="A33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B33" s="2">
         <v>45937</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E33">
         <v>625100</v>
@@ -5002,7 +5098,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M33">
         <v>44</v>
@@ -5017,84 +5113,81 @@
         <v>1</v>
       </c>
       <c r="AA33" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB33" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC33" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="AD33" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="AE33" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="AF33" t="s">
-        <v>214</v>
+        <v>257</v>
       </c>
       <c r="AJ33">
         <v>583</v>
       </c>
       <c r="AK33" t="s">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="AL33" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN33" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP33" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ33" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS33" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT33" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU33" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV33" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX33" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY33" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ33" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA33" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB33" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC33" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="34" spans="1:55">
+    <row r="34" spans="1:54">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B34" s="2">
         <v>45937</v>
       </c>
       <c r="C34" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E34">
         <v>625100</v>
@@ -5118,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M34">
         <v>44</v>
@@ -5133,84 +5226,81 @@
         <v>1</v>
       </c>
       <c r="AA34" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB34" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC34" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="AD34" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="AE34" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="AF34" t="s">
-        <v>215</v>
+        <v>258</v>
       </c>
       <c r="AJ34">
         <v>583</v>
       </c>
       <c r="AK34" t="s">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="AL34" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN34" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP34" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ34" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS34" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT34" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU34" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV34" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX34" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY34" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ34" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA34" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB34" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC34" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="35" spans="1:55">
+    <row r="35" spans="1:54">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B35" s="2">
         <v>45937</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E35">
         <v>625300</v>
@@ -5234,7 +5324,7 @@
         <v>1.42</v>
       </c>
       <c r="L35" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M35">
         <v>15.6</v>
@@ -5243,7 +5333,7 @@
         <v>14.18</v>
       </c>
       <c r="O35" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="P35">
         <v>1.42</v>
@@ -5261,90 +5351,87 @@
         <v>2</v>
       </c>
       <c r="AA35" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB35" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC35" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="AD35" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="AE35" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="AF35" t="s">
-        <v>216</v>
+        <v>259</v>
       </c>
       <c r="AH35" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AJ35">
         <v>584</v>
       </c>
       <c r="AK35" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="AL35" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN35" t="s">
-        <v>264</v>
+        <v>326</v>
       </c>
       <c r="AO35" t="s">
-        <v>266</v>
+        <v>329</v>
       </c>
       <c r="AP35" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ35" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS35" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT35" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU35" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV35" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX35" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY35" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ35" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA35" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB35" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC35" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="36" spans="1:55">
+    <row r="36" spans="1:54">
       <c r="A36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B36" s="2">
         <v>45937</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D36" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="E36">
         <v>625100</v>
@@ -5368,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M36">
         <v>46.4</v>
@@ -5377,7 +5464,7 @@
         <v>42.18</v>
       </c>
       <c r="O36" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="P36">
         <v>4.22</v>
@@ -5395,78 +5482,75 @@
         <v>1</v>
       </c>
       <c r="AA36" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB36" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC36" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="AD36" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="AJ36">
         <v>583</v>
       </c>
       <c r="AK36" t="s">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="AL36" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="AP36" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AQ36" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="AS36" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT36" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU36" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV36" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX36" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY36" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ36" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA36" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB36" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC36" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="37" spans="1:55">
+    <row r="37" spans="1:54">
       <c r="A37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B37" s="2">
         <v>45938</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E37">
         <v>625100</v>
@@ -5490,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M37">
         <v>64</v>
@@ -5505,84 +5589,81 @@
         <v>1</v>
       </c>
       <c r="AA37" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB37" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC37" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="AD37" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="AE37" t="s">
-        <v>191</v>
+        <v>230</v>
       </c>
       <c r="AF37" t="s">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="AG37" t="s">
-        <v>239</v>
+        <v>296</v>
       </c>
       <c r="AJ37">
         <v>580</v>
       </c>
       <c r="AK37" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="AL37" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN37" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="AP37" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AS37" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT37" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU37" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV37" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX37" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY37" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ37" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA37" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB37" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC37" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="38" spans="1:55">
+    <row r="38" spans="1:54">
       <c r="A38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B38" s="2">
         <v>45943</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D38" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="E38">
         <v>615100</v>
@@ -5606,7 +5687,7 @@
         <v>0</v>
       </c>
       <c r="L38" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M38">
         <v>5.62</v>
@@ -5621,75 +5702,72 @@
         <v>1</v>
       </c>
       <c r="AA38" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB38" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AD38" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="AF38" t="s">
-        <v>218</v>
+        <v>261</v>
       </c>
       <c r="AJ38">
         <v>651</v>
       </c>
       <c r="AK38" t="s">
-        <v>262</v>
+        <v>321</v>
       </c>
       <c r="AL38" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN38" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="AP38" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AS38" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT38" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU38" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV38" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX38" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY38" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ38" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA38" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB38" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC38" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="39" spans="1:55">
+    <row r="39" spans="1:54">
       <c r="A39" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B39" s="2">
         <v>45944</v>
       </c>
       <c r="C39" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E39">
         <v>625100</v>
@@ -5713,7 +5791,7 @@
         <v>0</v>
       </c>
       <c r="L39" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M39">
         <v>23.7</v>
@@ -5728,84 +5806,81 @@
         <v>1</v>
       </c>
       <c r="AA39" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB39" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC39" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="AD39" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="AE39" t="s">
-        <v>191</v>
+        <v>230</v>
       </c>
       <c r="AF39" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="AG39" t="s">
-        <v>240</v>
+        <v>297</v>
       </c>
       <c r="AJ39">
         <v>580</v>
       </c>
       <c r="AK39" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="AL39" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN39" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="AP39" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AS39" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT39" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU39" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV39" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX39" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY39" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ39" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA39" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB39" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC39" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="40" spans="1:55">
+    <row r="40" spans="1:54">
       <c r="A40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B40" s="2">
         <v>45944</v>
       </c>
       <c r="C40" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D40" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E40">
         <v>625300</v>
@@ -5829,7 +5904,7 @@
         <v>0.88</v>
       </c>
       <c r="L40" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M40">
         <v>16.9</v>
@@ -5838,7 +5913,7 @@
         <v>16.02</v>
       </c>
       <c r="O40" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="P40">
         <v>0.88</v>
@@ -5856,84 +5931,81 @@
         <v>1</v>
       </c>
       <c r="AA40" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB40" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC40" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="AD40" t="s">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="AE40" t="s">
-        <v>192</v>
+        <v>231</v>
       </c>
       <c r="AF40" t="s">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="AG40" t="s">
-        <v>241</v>
+        <v>298</v>
       </c>
       <c r="AJ40">
         <v>580</v>
       </c>
       <c r="AK40" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="AL40" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN40" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="AP40" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AS40" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT40" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU40" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV40" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX40" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY40" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ40" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA40" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB40" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC40" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="41" spans="1:55">
+    <row r="41" spans="1:54">
       <c r="A41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B41" s="2">
         <v>45945</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D41" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="E41">
         <v>615100</v>
@@ -5957,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M41">
         <v>5.56</v>
@@ -5972,75 +6044,72 @@
         <v>1</v>
       </c>
       <c r="AA41" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB41" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AD41" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="AF41" t="s">
-        <v>221</v>
+        <v>264</v>
       </c>
       <c r="AJ41">
         <v>651</v>
       </c>
       <c r="AK41" t="s">
-        <v>262</v>
+        <v>321</v>
       </c>
       <c r="AL41" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN41" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="AP41" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AS41" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT41" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU41" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV41" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX41" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY41" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ41" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA41" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB41" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC41" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="42" spans="1:55">
+    <row r="42" spans="1:54">
       <c r="A42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B42" s="2">
         <v>45945</v>
       </c>
       <c r="C42" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D42" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -6058,7 +6127,7 @@
         <v>12.22</v>
       </c>
       <c r="L42" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M42">
         <v>135.92</v>
@@ -6067,7 +6136,7 @@
         <v>123.7</v>
       </c>
       <c r="O42" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="P42">
         <v>12.22</v>
@@ -6082,81 +6151,78 @@
         <v>1</v>
       </c>
       <c r="AA42" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB42" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC42" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="AD42" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="AE42" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
       <c r="AF42" t="s">
-        <v>222</v>
+        <v>265</v>
       </c>
       <c r="AJ42">
         <v>580</v>
       </c>
       <c r="AK42" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="AL42" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN42" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="AP42" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AS42" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT42" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU42" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV42" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX42" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY42" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ42" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA42" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB42" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC42" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="43" spans="1:55">
+    <row r="43" spans="1:54">
       <c r="A43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B43" s="2">
         <v>45945</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E43">
         <v>625300</v>
@@ -6180,7 +6246,7 @@
         <v>1.5</v>
       </c>
       <c r="L43" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M43">
         <v>16.5</v>
@@ -6189,7 +6255,7 @@
         <v>15</v>
       </c>
       <c r="O43" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="P43">
         <v>1.5</v>
@@ -6207,81 +6273,78 @@
         <v>1</v>
       </c>
       <c r="AA43" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB43" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC43" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="AD43" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="AF43" t="s">
-        <v>223</v>
+        <v>266</v>
       </c>
       <c r="AG43" t="s">
-        <v>242</v>
+        <v>299</v>
       </c>
       <c r="AJ43">
         <v>580</v>
       </c>
       <c r="AK43" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="AL43" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN43" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="AP43" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AS43" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT43" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU43" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV43" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX43" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY43" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ43" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA43" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB43" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC43" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="44" spans="1:55">
+    <row r="44" spans="1:54">
       <c r="A44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B44" s="2">
         <v>45947</v>
       </c>
       <c r="C44" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E44">
         <v>625100</v>
@@ -6305,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="L44" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M44">
         <v>102</v>
@@ -6320,81 +6383,78 @@
         <v>1</v>
       </c>
       <c r="AA44" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB44" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC44" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="AD44" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="AE44" t="s">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="AF44" t="s">
-        <v>224</v>
+        <v>267</v>
       </c>
       <c r="AJ44">
         <v>580</v>
       </c>
       <c r="AK44" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="AL44" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN44" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="AP44" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AS44" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT44" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU44" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV44" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX44" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY44" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ44" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA44" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB44" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC44" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="45" spans="1:55">
+    <row r="45" spans="1:54">
       <c r="A45" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B45" s="2">
         <v>45953</v>
       </c>
       <c r="C45" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="E45">
         <v>615100</v>
@@ -6418,7 +6478,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M45">
         <v>11.39</v>
@@ -6433,75 +6493,72 @@
         <v>1</v>
       </c>
       <c r="AA45" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB45" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AD45" t="s">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="AF45" t="s">
-        <v>225</v>
+        <v>268</v>
       </c>
       <c r="AJ45">
         <v>651</v>
       </c>
       <c r="AK45" t="s">
-        <v>262</v>
+        <v>321</v>
       </c>
       <c r="AL45" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN45" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="AP45" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AS45" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT45" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU45" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV45" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX45" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY45" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ45" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA45" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB45" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC45" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="46" spans="1:55">
+    <row r="46" spans="1:54">
       <c r="A46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B46" s="2">
         <v>45953</v>
       </c>
       <c r="C46" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="D46" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E46">
         <v>625300</v>
@@ -6525,7 +6582,7 @@
         <v>0.37</v>
       </c>
       <c r="L46" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M46">
         <v>4.9</v>
@@ -6534,7 +6591,7 @@
         <v>4.53</v>
       </c>
       <c r="O46" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="P46">
         <v>0.1</v>
@@ -6543,7 +6600,7 @@
         <v>445660</v>
       </c>
       <c r="R46" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="S46">
         <v>0.27</v>
@@ -6561,84 +6618,81 @@
         <v>1</v>
       </c>
       <c r="AA46" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB46" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC46" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="AD46" t="s">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="AE46" t="s">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="AF46" t="s">
-        <v>226</v>
+        <v>269</v>
       </c>
       <c r="AG46" t="s">
-        <v>243</v>
+        <v>300</v>
       </c>
       <c r="AJ46">
         <v>580</v>
       </c>
       <c r="AK46" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="AL46" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN46" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="AP46" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AS46" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT46" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU46" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV46" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX46" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY46" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ46" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA46" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB46" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC46" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="47" spans="1:55">
+    <row r="47" spans="1:54">
       <c r="A47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B47" s="2">
         <v>45953</v>
       </c>
       <c r="C47" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D47" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E47">
         <v>625300</v>
@@ -6662,7 +6716,7 @@
         <v>2.23</v>
       </c>
       <c r="L47" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M47">
         <v>24.5</v>
@@ -6671,7 +6725,7 @@
         <v>22.27</v>
       </c>
       <c r="O47" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="P47">
         <v>2.23</v>
@@ -6689,81 +6743,78 @@
         <v>1</v>
       </c>
       <c r="AA47" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB47" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC47" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="AD47" t="s">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="AF47" t="s">
-        <v>227</v>
+        <v>270</v>
       </c>
       <c r="AG47" t="s">
-        <v>242</v>
+        <v>299</v>
       </c>
       <c r="AJ47">
         <v>580</v>
       </c>
       <c r="AK47" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="AL47" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN47" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="AP47" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AS47" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT47" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU47" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV47" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX47" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY47" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ47" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA47" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB47" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC47" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="48" spans="1:55">
+    <row r="48" spans="1:54">
       <c r="A48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B48" s="2">
         <v>45960</v>
       </c>
       <c r="C48" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="D48" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="E48">
         <v>615100</v>
@@ -6787,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="L48" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M48">
         <v>11.26</v>
@@ -6802,72 +6853,69 @@
         <v>1</v>
       </c>
       <c r="AA48" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB48" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AD48" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="AJ48">
         <v>651</v>
       </c>
       <c r="AK48" t="s">
-        <v>262</v>
+        <v>321</v>
       </c>
       <c r="AL48" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN48" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="AP48" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AS48" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT48" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU48" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV48" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="AX48" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AY48" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="AZ48" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BA48" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="BB48" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC48" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="49" spans="1:55">
+    <row r="49" spans="1:54">
       <c r="A49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B49" s="2">
         <v>45960</v>
       </c>
       <c r="C49" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="D49" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E49">
         <v>625300</v>
@@ -6891,7 +6939,7 @@
         <v>1.73</v>
       </c>
       <c r="L49" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="M49">
         <v>19</v>
@@ -6900,7 +6948,7 @@
         <v>17.27</v>
       </c>
       <c r="O49" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="P49">
         <v>1.73</v>
@@ -6918,70 +6966,1885 @@
         <v>1</v>
       </c>
       <c r="AA49" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB49" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC49" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="AD49" t="s">
-        <v>184</v>
+        <v>217</v>
       </c>
       <c r="AE49" t="s">
-        <v>196</v>
+        <v>235</v>
       </c>
       <c r="AF49" t="s">
-        <v>228</v>
+        <v>271</v>
       </c>
       <c r="AG49" t="s">
-        <v>242</v>
+        <v>299</v>
       </c>
       <c r="AJ49">
         <v>580</v>
       </c>
       <c r="AK49" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="AL49" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="AN49" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="AP49" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="AS49" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AT49" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="AU49" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="AV49" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX49" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY49" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ49" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA49" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB49" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="50" spans="1:54">
+      <c r="A50" t="s">
+        <v>102</v>
+      </c>
+      <c r="B50" s="2">
+        <v>45977</v>
+      </c>
+      <c r="C50" t="s">
+        <v>148</v>
+      </c>
+      <c r="D50" t="s">
+        <v>158</v>
+      </c>
+      <c r="E50">
+        <v>625100</v>
+      </c>
+      <c r="F50">
+        <v>445660</v>
+      </c>
+      <c r="H50">
+        <v>26.1</v>
+      </c>
+      <c r="I50">
+        <v>26.1</v>
+      </c>
+      <c r="J50">
+        <v>26.1</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50" t="s">
+        <v>164</v>
+      </c>
+      <c r="M50">
+        <v>26.1</v>
+      </c>
+      <c r="N50">
+        <v>26.1</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>1</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>178</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>207</v>
+      </c>
+      <c r="AE50" t="s">
+        <v>230</v>
+      </c>
+      <c r="AF50" t="s">
         <v>272</v>
       </c>
-      <c r="AX49" t="s">
+      <c r="AJ50">
+        <v>655</v>
+      </c>
+      <c r="AK50" t="s">
+        <v>322</v>
+      </c>
+      <c r="AL50" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>328</v>
+      </c>
+      <c r="AO50" t="s">
+        <v>330</v>
+      </c>
+      <c r="AP50" t="s">
+        <v>331</v>
+      </c>
+      <c r="AQ50" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS50" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT50" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU50" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV50" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX50" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY50" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ50" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA50" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB50" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="51" spans="1:54">
+      <c r="A51" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" s="2">
+        <v>45978</v>
+      </c>
+      <c r="C51" t="s">
+        <v>149</v>
+      </c>
+      <c r="D51" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51">
+        <v>625100</v>
+      </c>
+      <c r="F51">
+        <v>445660</v>
+      </c>
+      <c r="H51">
+        <v>15</v>
+      </c>
+      <c r="I51">
+        <v>15</v>
+      </c>
+      <c r="J51">
+        <v>15</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51" t="s">
+        <v>164</v>
+      </c>
+      <c r="M51">
+        <v>15</v>
+      </c>
+      <c r="N51">
+        <v>13.64</v>
+      </c>
+      <c r="O51" t="s">
+        <v>165</v>
+      </c>
+      <c r="P51">
+        <v>1.36</v>
+      </c>
+      <c r="Q51">
+        <v>445660</v>
+      </c>
+      <c r="X51">
+        <v>1.36</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>1</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>185</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>218</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>236</v>
+      </c>
+      <c r="AF51" t="s">
+        <v>273</v>
+      </c>
+      <c r="AJ51">
+        <v>655</v>
+      </c>
+      <c r="AK51" t="s">
+        <v>322</v>
+      </c>
+      <c r="AL51" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN51" t="s">
+        <v>328</v>
+      </c>
+      <c r="AO51" t="s">
+        <v>330</v>
+      </c>
+      <c r="AP51" t="s">
+        <v>331</v>
+      </c>
+      <c r="AQ51" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS51" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT51" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU51" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV51" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX51" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY51" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ51" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA51" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB51" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="52" spans="1:54">
+      <c r="A52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" s="2">
+        <v>45978</v>
+      </c>
+      <c r="C52" t="s">
+        <v>150</v>
+      </c>
+      <c r="D52" t="s">
         <v>160</v>
       </c>
-      <c r="AY49" t="s">
+      <c r="E52">
+        <v>625300</v>
+      </c>
+      <c r="F52">
+        <v>445660</v>
+      </c>
+      <c r="H52">
+        <v>7.84</v>
+      </c>
+      <c r="I52">
+        <v>7.84</v>
+      </c>
+      <c r="J52">
+        <v>7.15</v>
+      </c>
+      <c r="K52">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L52" t="s">
+        <v>164</v>
+      </c>
+      <c r="M52">
+        <v>7.84</v>
+      </c>
+      <c r="N52">
+        <v>7.15</v>
+      </c>
+      <c r="O52" t="s">
+        <v>165</v>
+      </c>
+      <c r="P52">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q52">
+        <v>445660</v>
+      </c>
+      <c r="X52">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>1</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>172</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>197</v>
+      </c>
+      <c r="AE52" t="s">
+        <v>226</v>
+      </c>
+      <c r="AF52" t="s">
         <v>274</v>
       </c>
-      <c r="AZ49" t="s">
-        <v>272</v>
-      </c>
-      <c r="BA49" t="s">
-        <v>272</v>
-      </c>
-      <c r="BB49" t="s">
+      <c r="AJ52">
+        <v>655</v>
+      </c>
+      <c r="AK52" t="s">
+        <v>322</v>
+      </c>
+      <c r="AL52" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN52" t="s">
+        <v>328</v>
+      </c>
+      <c r="AO52" t="s">
+        <v>330</v>
+      </c>
+      <c r="AP52" t="s">
+        <v>331</v>
+      </c>
+      <c r="AQ52" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS52" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT52" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU52" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV52" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX52" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY52" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ52" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA52" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB52" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="53" spans="1:54">
+      <c r="A53" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" s="2">
+        <v>45978</v>
+      </c>
+      <c r="C53" t="s">
+        <v>151</v>
+      </c>
+      <c r="D53" t="s">
+        <v>160</v>
+      </c>
+      <c r="E53">
+        <v>625300</v>
+      </c>
+      <c r="F53">
+        <v>445660</v>
+      </c>
+      <c r="H53">
+        <v>26.8</v>
+      </c>
+      <c r="I53">
+        <v>26.8</v>
+      </c>
+      <c r="J53">
+        <v>24.36</v>
+      </c>
+      <c r="K53">
+        <v>2.44</v>
+      </c>
+      <c r="L53" t="s">
+        <v>164</v>
+      </c>
+      <c r="M53">
+        <v>26.8</v>
+      </c>
+      <c r="N53">
+        <v>24.36</v>
+      </c>
+      <c r="O53" t="s">
+        <v>165</v>
+      </c>
+      <c r="P53">
+        <v>2.44</v>
+      </c>
+      <c r="Q53">
+        <v>445660</v>
+      </c>
+      <c r="X53">
+        <v>2.44</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <v>1</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>186</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>193</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>237</v>
+      </c>
+      <c r="AF53" t="s">
         <v>275</v>
       </c>
-      <c r="BC49" t="s">
-        <v>272</v>
+      <c r="AJ53">
+        <v>655</v>
+      </c>
+      <c r="AK53" t="s">
+        <v>322</v>
+      </c>
+      <c r="AL53" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN53" t="s">
+        <v>328</v>
+      </c>
+      <c r="AO53" t="s">
+        <v>330</v>
+      </c>
+      <c r="AP53" t="s">
+        <v>331</v>
+      </c>
+      <c r="AQ53" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS53" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT53" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU53" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV53" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX53" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY53" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ53" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA53" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB53" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="54" spans="1:54">
+      <c r="A54" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" s="2">
+        <v>45979</v>
+      </c>
+      <c r="C54" t="s">
+        <v>152</v>
+      </c>
+      <c r="D54" t="s">
+        <v>162</v>
+      </c>
+      <c r="H54">
+        <v>121.25</v>
+      </c>
+      <c r="I54">
+        <v>121.25</v>
+      </c>
+      <c r="J54">
+        <v>110.39</v>
+      </c>
+      <c r="K54">
+        <v>10.86</v>
+      </c>
+      <c r="L54" t="s">
+        <v>164</v>
+      </c>
+      <c r="M54">
+        <v>121.25</v>
+      </c>
+      <c r="N54">
+        <v>110.39</v>
+      </c>
+      <c r="O54" t="s">
+        <v>165</v>
+      </c>
+      <c r="P54">
+        <v>10.86</v>
+      </c>
+      <c r="X54">
+        <v>10.86</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>1</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>187</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>219</v>
+      </c>
+      <c r="AE54" t="s">
+        <v>238</v>
+      </c>
+      <c r="AF54" t="s">
+        <v>276</v>
+      </c>
+      <c r="AJ54">
+        <v>655</v>
+      </c>
+      <c r="AK54" t="s">
+        <v>322</v>
+      </c>
+      <c r="AL54" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN54" t="s">
+        <v>328</v>
+      </c>
+      <c r="AO54" t="s">
+        <v>330</v>
+      </c>
+      <c r="AP54" t="s">
+        <v>331</v>
+      </c>
+      <c r="AQ54" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS54" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT54" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU54" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV54" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX54" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY54" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ54" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA54" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB54" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="55" spans="1:54">
+      <c r="A55" t="s">
+        <v>107</v>
+      </c>
+      <c r="B55" s="2">
+        <v>45979</v>
+      </c>
+      <c r="C55" t="s">
+        <v>153</v>
+      </c>
+      <c r="D55" t="s">
+        <v>118</v>
+      </c>
+      <c r="E55">
+        <v>625100</v>
+      </c>
+      <c r="F55">
+        <v>445660</v>
+      </c>
+      <c r="H55">
+        <v>45</v>
+      </c>
+      <c r="I55">
+        <v>45</v>
+      </c>
+      <c r="J55">
+        <v>45</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55" t="s">
+        <v>164</v>
+      </c>
+      <c r="M55">
+        <v>45</v>
+      </c>
+      <c r="N55">
+        <v>40.91</v>
+      </c>
+      <c r="O55" t="s">
+        <v>165</v>
+      </c>
+      <c r="P55">
+        <v>4.09</v>
+      </c>
+      <c r="Q55">
+        <v>445660</v>
+      </c>
+      <c r="X55">
+        <v>4.09</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <v>1</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>185</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>218</v>
+      </c>
+      <c r="AE55" t="s">
+        <v>236</v>
+      </c>
+      <c r="AF55" t="s">
+        <v>277</v>
+      </c>
+      <c r="AJ55">
+        <v>655</v>
+      </c>
+      <c r="AK55" t="s">
+        <v>322</v>
+      </c>
+      <c r="AL55" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN55" t="s">
+        <v>328</v>
+      </c>
+      <c r="AO55" t="s">
+        <v>330</v>
+      </c>
+      <c r="AP55" t="s">
+        <v>331</v>
+      </c>
+      <c r="AQ55" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS55" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT55" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU55" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV55" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX55" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY55" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ55" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA55" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB55" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="56" spans="1:54">
+      <c r="A56" t="s">
+        <v>108</v>
+      </c>
+      <c r="B56" s="2">
+        <v>45986</v>
+      </c>
+      <c r="C56" t="s">
+        <v>154</v>
+      </c>
+      <c r="D56" t="s">
+        <v>161</v>
+      </c>
+      <c r="E56">
+        <v>615100</v>
+      </c>
+      <c r="F56">
+        <v>445660</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>201.63</v>
+      </c>
+      <c r="J56">
+        <v>201.63</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56" t="s">
+        <v>164</v>
+      </c>
+      <c r="M56">
+        <v>201.63</v>
+      </c>
+      <c r="N56">
+        <v>201.63</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>1</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>193</v>
+      </c>
+      <c r="AG56" t="s">
+        <v>301</v>
+      </c>
+      <c r="AJ56">
+        <v>658</v>
+      </c>
+      <c r="AK56" t="s">
+        <v>323</v>
+      </c>
+      <c r="AL56" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN56" t="s">
+        <v>326</v>
+      </c>
+      <c r="AO56" t="s">
+        <v>329</v>
+      </c>
+      <c r="AP56" t="s">
+        <v>331</v>
+      </c>
+      <c r="AQ56" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS56" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT56" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU56" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV56" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX56" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY56" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ56" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA56" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB56" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="57" spans="1:54">
+      <c r="A57" t="s">
+        <v>109</v>
+      </c>
+      <c r="B57" s="2">
+        <v>45986</v>
+      </c>
+      <c r="C57" t="s">
+        <v>155</v>
+      </c>
+      <c r="D57" t="s">
+        <v>163</v>
+      </c>
+      <c r="E57">
+        <v>625100</v>
+      </c>
+      <c r="F57">
+        <v>445660</v>
+      </c>
+      <c r="H57">
+        <v>6.9</v>
+      </c>
+      <c r="I57">
+        <v>6.9</v>
+      </c>
+      <c r="J57">
+        <v>5.75</v>
+      </c>
+      <c r="K57">
+        <v>1.15</v>
+      </c>
+      <c r="L57" t="s">
+        <v>164</v>
+      </c>
+      <c r="M57">
+        <v>6.9</v>
+      </c>
+      <c r="N57">
+        <v>5.75</v>
+      </c>
+      <c r="O57" t="s">
+        <v>167</v>
+      </c>
+      <c r="P57">
+        <v>1.15</v>
+      </c>
+      <c r="Q57">
+        <v>445660</v>
+      </c>
+      <c r="X57">
+        <v>1.15</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>1</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB57" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC57" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD57" t="s">
+        <v>220</v>
+      </c>
+      <c r="AF57" t="s">
+        <v>278</v>
+      </c>
+      <c r="AG57" t="s">
+        <v>156</v>
+      </c>
+      <c r="AJ57">
+        <v>658</v>
+      </c>
+      <c r="AK57" t="s">
+        <v>323</v>
+      </c>
+      <c r="AL57" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN57" t="s">
+        <v>326</v>
+      </c>
+      <c r="AO57" t="s">
+        <v>329</v>
+      </c>
+      <c r="AP57" t="s">
+        <v>331</v>
+      </c>
+      <c r="AQ57" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS57" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT57" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU57" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV57" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX57" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY57" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ57" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA57" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB57" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="58" spans="1:54">
+      <c r="A58" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" s="2">
+        <v>45986</v>
+      </c>
+      <c r="C58" t="s">
+        <v>156</v>
+      </c>
+      <c r="D58" t="s">
+        <v>163</v>
+      </c>
+      <c r="E58">
+        <v>625100</v>
+      </c>
+      <c r="F58">
+        <v>445660</v>
+      </c>
+      <c r="H58">
+        <v>6.9</v>
+      </c>
+      <c r="I58">
+        <v>6.9</v>
+      </c>
+      <c r="J58">
+        <v>5.75</v>
+      </c>
+      <c r="K58">
+        <v>1.15</v>
+      </c>
+      <c r="L58" t="s">
+        <v>164</v>
+      </c>
+      <c r="M58">
+        <v>6.9</v>
+      </c>
+      <c r="N58">
+        <v>5.75</v>
+      </c>
+      <c r="O58" t="s">
+        <v>167</v>
+      </c>
+      <c r="P58">
+        <v>1.15</v>
+      </c>
+      <c r="Q58">
+        <v>445660</v>
+      </c>
+      <c r="X58">
+        <v>1.15</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>1</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB58" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC58" t="s">
+        <v>189</v>
+      </c>
+      <c r="AD58" t="s">
+        <v>221</v>
+      </c>
+      <c r="AF58" t="s">
+        <v>279</v>
+      </c>
+      <c r="AG58" t="s">
+        <v>156</v>
+      </c>
+      <c r="AJ58">
+        <v>658</v>
+      </c>
+      <c r="AK58" t="s">
+        <v>323</v>
+      </c>
+      <c r="AL58" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN58" t="s">
+        <v>326</v>
+      </c>
+      <c r="AO58" t="s">
+        <v>329</v>
+      </c>
+      <c r="AP58" t="s">
+        <v>331</v>
+      </c>
+      <c r="AQ58" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS58" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT58" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU58" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV58" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX58" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY58" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ58" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA58" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB58" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="59" spans="1:54">
+      <c r="A59" t="s">
+        <v>111</v>
+      </c>
+      <c r="B59" s="2">
+        <v>45986</v>
+      </c>
+      <c r="C59" t="s">
+        <v>118</v>
+      </c>
+      <c r="D59" t="s">
+        <v>118</v>
+      </c>
+      <c r="E59">
+        <v>625100</v>
+      </c>
+      <c r="F59">
+        <v>445660</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>38.2</v>
+      </c>
+      <c r="I59">
+        <v>38.2</v>
+      </c>
+      <c r="J59">
+        <v>38.2</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59" t="s">
+        <v>164</v>
+      </c>
+      <c r="M59">
+        <v>38.2</v>
+      </c>
+      <c r="N59">
+        <v>34.73</v>
+      </c>
+      <c r="O59" t="s">
+        <v>165</v>
+      </c>
+      <c r="P59">
+        <v>3.47</v>
+      </c>
+      <c r="Q59">
+        <v>445660</v>
+      </c>
+      <c r="X59">
+        <v>3.47</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>1</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB59" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC59" t="s">
+        <v>190</v>
+      </c>
+      <c r="AD59" t="s">
+        <v>222</v>
+      </c>
+      <c r="AE59" t="s">
+        <v>239</v>
+      </c>
+      <c r="AF59" t="s">
+        <v>280</v>
+      </c>
+      <c r="AJ59">
+        <v>661</v>
+      </c>
+      <c r="AK59" t="s">
+        <v>324</v>
+      </c>
+      <c r="AL59" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN59" t="s">
+        <v>303</v>
+      </c>
+      <c r="AP59" t="s">
+        <v>331</v>
+      </c>
+      <c r="AQ59" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS59" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT59" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU59" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV59" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX59" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY59" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ59" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA59" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB59" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="60" spans="1:54">
+      <c r="A60" t="s">
+        <v>112</v>
+      </c>
+      <c r="B60" s="2">
+        <v>45986</v>
+      </c>
+      <c r="C60" t="s">
+        <v>157</v>
+      </c>
+      <c r="D60" t="s">
+        <v>158</v>
+      </c>
+      <c r="E60">
+        <v>625100</v>
+      </c>
+      <c r="F60">
+        <v>445660</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>44</v>
+      </c>
+      <c r="I60">
+        <v>44</v>
+      </c>
+      <c r="J60">
+        <v>44</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60" t="s">
+        <v>164</v>
+      </c>
+      <c r="M60">
+        <v>44</v>
+      </c>
+      <c r="N60">
+        <v>44</v>
+      </c>
+      <c r="Y60">
+        <v>0</v>
+      </c>
+      <c r="Z60">
+        <v>1</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB60" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC60" t="s">
+        <v>171</v>
+      </c>
+      <c r="AD60" t="s">
+        <v>195</v>
+      </c>
+      <c r="AE60" t="s">
+        <v>225</v>
+      </c>
+      <c r="AF60" t="s">
+        <v>281</v>
+      </c>
+      <c r="AJ60">
+        <v>661</v>
+      </c>
+      <c r="AK60" t="s">
+        <v>324</v>
+      </c>
+      <c r="AL60" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN60" t="s">
+        <v>303</v>
+      </c>
+      <c r="AP60" t="s">
+        <v>331</v>
+      </c>
+      <c r="AQ60" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS60" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT60" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU60" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV60" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX60" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY60" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ60" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA60" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB60" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="61" spans="1:54">
+      <c r="A61" t="s">
+        <v>113</v>
+      </c>
+      <c r="B61" s="2">
+        <v>45986</v>
+      </c>
+      <c r="C61" t="s">
+        <v>157</v>
+      </c>
+      <c r="D61" t="s">
+        <v>158</v>
+      </c>
+      <c r="E61">
+        <v>625100</v>
+      </c>
+      <c r="F61">
+        <v>445660</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>44</v>
+      </c>
+      <c r="I61">
+        <v>44</v>
+      </c>
+      <c r="J61">
+        <v>44</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61" t="s">
+        <v>164</v>
+      </c>
+      <c r="M61">
+        <v>44</v>
+      </c>
+      <c r="N61">
+        <v>44</v>
+      </c>
+      <c r="Y61">
+        <v>0</v>
+      </c>
+      <c r="Z61">
+        <v>1</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB61" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC61" t="s">
+        <v>171</v>
+      </c>
+      <c r="AD61" t="s">
+        <v>195</v>
+      </c>
+      <c r="AE61" t="s">
+        <v>225</v>
+      </c>
+      <c r="AF61" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ61">
+        <v>661</v>
+      </c>
+      <c r="AK61" t="s">
+        <v>324</v>
+      </c>
+      <c r="AL61" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN61" t="s">
+        <v>303</v>
+      </c>
+      <c r="AP61" t="s">
+        <v>331</v>
+      </c>
+      <c r="AQ61" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS61" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT61" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU61" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV61" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX61" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY61" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ61" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA61" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB61" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="62" spans="1:54">
+      <c r="A62" t="s">
+        <v>114</v>
+      </c>
+      <c r="B62" s="2">
+        <v>45986</v>
+      </c>
+      <c r="C62" t="s">
+        <v>131</v>
+      </c>
+      <c r="D62" t="s">
+        <v>160</v>
+      </c>
+      <c r="E62">
+        <v>625300</v>
+      </c>
+      <c r="F62">
+        <v>445660</v>
+      </c>
+      <c r="H62">
+        <v>27.25</v>
+      </c>
+      <c r="I62">
+        <v>27.25</v>
+      </c>
+      <c r="J62">
+        <v>24.76</v>
+      </c>
+      <c r="K62">
+        <v>2.49</v>
+      </c>
+      <c r="L62" t="s">
+        <v>164</v>
+      </c>
+      <c r="M62">
+        <v>27.25</v>
+      </c>
+      <c r="N62">
+        <v>24.76</v>
+      </c>
+      <c r="O62" t="s">
+        <v>165</v>
+      </c>
+      <c r="P62">
+        <v>2.49</v>
+      </c>
+      <c r="Q62">
+        <v>445660</v>
+      </c>
+      <c r="X62">
+        <v>2.49</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+      <c r="Z62">
+        <v>3</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB62" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC62" t="s">
+        <v>172</v>
+      </c>
+      <c r="AD62" t="s">
+        <v>197</v>
+      </c>
+      <c r="AE62" t="s">
+        <v>226</v>
+      </c>
+      <c r="AF62" t="s">
+        <v>283</v>
+      </c>
+      <c r="AG62" t="s">
+        <v>302</v>
+      </c>
+      <c r="AH62" t="s">
+        <v>303</v>
+      </c>
+      <c r="AI62" t="s">
+        <v>305</v>
+      </c>
+      <c r="AJ62">
+        <v>658</v>
+      </c>
+      <c r="AK62" t="s">
+        <v>323</v>
+      </c>
+      <c r="AL62" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN62" t="s">
+        <v>326</v>
+      </c>
+      <c r="AO62" t="s">
+        <v>329</v>
+      </c>
+      <c r="AP62" t="s">
+        <v>331</v>
+      </c>
+      <c r="AQ62" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS62" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT62" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU62" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV62" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX62" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY62" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ62" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA62" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB62" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="63" spans="1:54">
+      <c r="A63" t="s">
+        <v>115</v>
+      </c>
+      <c r="B63" s="2">
+        <v>45986</v>
+      </c>
+      <c r="C63" t="s">
+        <v>118</v>
+      </c>
+      <c r="D63" t="s">
+        <v>118</v>
+      </c>
+      <c r="E63">
+        <v>625100</v>
+      </c>
+      <c r="F63">
+        <v>445660</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>36.8</v>
+      </c>
+      <c r="I63">
+        <v>36.8</v>
+      </c>
+      <c r="J63">
+        <v>36.8</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63" t="s">
+        <v>164</v>
+      </c>
+      <c r="M63">
+        <v>36.8</v>
+      </c>
+      <c r="N63">
+        <v>33.45</v>
+      </c>
+      <c r="O63" t="s">
+        <v>165</v>
+      </c>
+      <c r="P63">
+        <v>3.35</v>
+      </c>
+      <c r="Q63">
+        <v>445660</v>
+      </c>
+      <c r="X63">
+        <v>3.35</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
+        <v>1</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB63" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC63" t="s">
+        <v>176</v>
+      </c>
+      <c r="AD63" t="s">
+        <v>203</v>
+      </c>
+      <c r="AF63" t="s">
+        <v>284</v>
+      </c>
+      <c r="AJ63">
+        <v>661</v>
+      </c>
+      <c r="AK63" t="s">
+        <v>324</v>
+      </c>
+      <c r="AL63" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN63" t="s">
+        <v>303</v>
+      </c>
+      <c r="AP63" t="s">
+        <v>331</v>
+      </c>
+      <c r="AQ63" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS63" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT63" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU63" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV63" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX63" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY63" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ63" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA63" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB63" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="64" spans="1:54">
+      <c r="A64" t="s">
+        <v>116</v>
+      </c>
+      <c r="B64" s="2">
+        <v>45986</v>
+      </c>
+      <c r="C64" t="s">
+        <v>156</v>
+      </c>
+      <c r="D64" t="s">
+        <v>163</v>
+      </c>
+      <c r="E64">
+        <v>625100</v>
+      </c>
+      <c r="F64">
+        <v>445660</v>
+      </c>
+      <c r="H64">
+        <v>3.7</v>
+      </c>
+      <c r="I64">
+        <v>3.7</v>
+      </c>
+      <c r="J64">
+        <v>3.08</v>
+      </c>
+      <c r="K64">
+        <v>0.62</v>
+      </c>
+      <c r="L64" t="s">
+        <v>164</v>
+      </c>
+      <c r="M64">
+        <v>3.7</v>
+      </c>
+      <c r="N64">
+        <v>3.08</v>
+      </c>
+      <c r="O64" t="s">
+        <v>167</v>
+      </c>
+      <c r="P64">
+        <v>0.62</v>
+      </c>
+      <c r="Q64">
+        <v>445660</v>
+      </c>
+      <c r="X64">
+        <v>0.62</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>1</v>
+      </c>
+      <c r="AA64" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB64" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC64" t="s">
+        <v>191</v>
+      </c>
+      <c r="AD64" t="s">
+        <v>223</v>
+      </c>
+      <c r="AF64" t="s">
+        <v>285</v>
+      </c>
+      <c r="AG64" t="s">
+        <v>156</v>
+      </c>
+      <c r="AJ64">
+        <v>658</v>
+      </c>
+      <c r="AK64" t="s">
+        <v>323</v>
+      </c>
+      <c r="AL64" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN64" t="s">
+        <v>326</v>
+      </c>
+      <c r="AO64" t="s">
+        <v>329</v>
+      </c>
+      <c r="AP64" t="s">
+        <v>331</v>
+      </c>
+      <c r="AQ64" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS64" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT64" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU64" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV64" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX64" t="s">
+        <v>193</v>
+      </c>
+      <c r="AY64" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ64" t="s">
+        <v>336</v>
+      </c>
+      <c r="BA64" t="s">
+        <v>336</v>
+      </c>
+      <c r="BB64" t="s">
+        <v>339</v>
       </c>
     </row>
   </sheetData>
